--- a/kostock/s50_principles/나만의기법/종목리스트.xlsx
+++ b/kostock/s50_principles/나만의기법/종목리스트.xlsx
@@ -12,7 +12,7 @@
     <x:workbookView xWindow="0" yWindow="0" windowWidth="21345" windowHeight="9945"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <x:sheet name="환율관련" sheetId="1" r:id="rId4"/>
   </x:sheets>
   <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
 </x:workbook>
@@ -21,12 +21,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="86">
   <x:si>
-    <x:t>■ 환률하락 수혜테마</x:t>
-  </x:si>
-  <x:si>
-    <x:t>■ 환률상승 수혜테마</x:t>
-  </x:si>
-  <x:si>
     <x:t>종목명</x:t>
   </x:si>
   <x:si>
@@ -160,6 +154,12 @@
   </x:si>
   <x:si>
     <x:t>한탑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>■ 환율상승 수혜테마</x:t>
+  </x:si>
+  <x:si>
+    <x:t>■ 환율하락 수혜테마</x:t>
   </x:si>
   <x:si>
     <x:t>대한항공</x:t>
@@ -737,164 +737,164 @@
   <x:sheetData>
     <x:row r="1" spans="1:1">
       <x:c r="A1" t="s">
-        <x:v>1</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="2:3">
       <x:c r="B2" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="2:3">
       <x:c r="B3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C3" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="2:3">
       <x:c r="B4" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="2:3">
       <x:c r="B5" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="2:3">
       <x:c r="B6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="2:3">
       <x:c r="B7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="2:3">
       <x:c r="B8" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C8" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:3">
       <x:c r="B9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="2:3">
       <x:c r="B10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="2:3">
       <x:c r="B11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="2:3">
       <x:c r="B12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="2:3">
       <x:c r="B13" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="2:3">
       <x:c r="B14" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="2:3">
       <x:c r="B15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C15" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="2:3">
       <x:c r="B16" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C16" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="2:3">
       <x:c r="B17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C17" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="2:3">
       <x:c r="B18" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C18" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="2:3">
       <x:c r="B19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C19" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="2:3">
       <x:c r="B20" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C20" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B23" s="5"/>
       <x:c r="C23" s="6"/>
@@ -902,10 +902,10 @@
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="5"/>
       <x:c r="B24" s="7" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C24" s="7" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -947,7 +947,7 @@
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="5"/>
       <x:c r="B29" s="8" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C29" s="9" t="s">
         <x:v>60</x:v>
@@ -956,7 +956,7 @@
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="5"/>
       <x:c r="B30" s="8" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C30" s="9" t="s">
         <x:v>56</x:v>
@@ -992,10 +992,10 @@
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="5"/>
       <x:c r="B34" s="8" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C34" s="9" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
@@ -1037,7 +1037,7 @@
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="5"/>
       <x:c r="B39" s="8" t="s">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C39" s="9" t="s">
         <x:v>48</x:v>
@@ -1046,7 +1046,7 @@
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="5"/>
       <x:c r="B40" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C40" s="9" t="s">
         <x:v>51</x:v>
@@ -1055,7 +1055,7 @@
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="5"/>
       <x:c r="B41" s="8" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C41" s="9" t="s">
         <x:v>57</x:v>
@@ -1096,7 +1096,7 @@
     </x:row>
     <x:row r="46" spans="2:3">
       <x:c r="B46" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C46" s="9" t="s">
         <x:v>84</x:v>
@@ -1112,7 +1112,7 @@
     </x:row>
     <x:row r="48" spans="2:3">
       <x:c r="B48" s="8" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C48" s="9" t="s">
         <x:v>79</x:v>
